--- a/plantillas/consulta/Validacion_Resultados.xlsx
+++ b/plantillas/consulta/Validacion_Resultados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C912FC-E527-441D-91E8-5CF0E68A822E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B20E85F-455F-4EA8-B3E5-0A5F7EB39C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -590,7 +590,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
@@ -653,11 +653,13 @@
       <c r="B8" s="6"/>
       <c r="D8" s="1"/>
       <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="D9" s="1"/>
       <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>

--- a/plantillas/consulta/Validacion_Resultados.xlsx
+++ b/plantillas/consulta/Validacion_Resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B20E85F-455F-4EA8-B3E5-0A5F7EB39C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83D9212-E53C-432F-B79F-4F56573E9D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 (Las marcadas con la palabra "voto" en la Lista nominal y las que opinaron con resoluciones del Tribunal Electoral)</t>
   </si>
   <si>
-    <t>Total de personas que votaron
+    <t>Total de personas que emitieron su opinión
 (EN CASO DE ACTAS LEVANTADAS EN DIRECCIÓN DISTRITAL)</t>
   </si>
 </sst>

--- a/plantillas/consulta/Validacion_Resultados.xlsx
+++ b/plantillas/consulta/Validacion_Resultados.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83D9212-E53C-432F-B79F-4F56573E9D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
